--- a/docs/计算-光伏阵列-深圳.xlsx
+++ b/docs/计算-光伏阵列-深圳.xlsx
@@ -430,8 +430,932 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r='1'><c r='A1' t='inlineStr'><is><t>PV array capacity calc and checks (Shenzhen W5, auto)</t></is></c></row><row r='2'><c r='A2' t='inlineStr'><is><t>Item</t></is></c><c r='B2' t='inlineStr'><is><t>Formula/Value</t></is></c><c r='C2' t='inlineStr'><is><t>Note</t></is></c></row><row r='3'><c r='A3' t='inlineStr'><is><t>P_PV,min (kWp)</t></is></c><c r='B3'><f>='Parameters'!B3*'Parameters'!B4/('Parameters'!B5*'Parameters'!B6)</f></c><c r='C3' t='inlineStr'><is><t>E_AC*K_PV/(H_tilt*eta_path)</t></is></c></row><row r='4'><c r='A4' t='inlineStr'><is><t>Voc,cold (V)</t></is></c><c r='B4'><f>='Parameters'!B11*(1+'Parameters'!B15*('Parameters'!B7-25))</f></c><c r='C4' t='inlineStr'><is><t>per module</t></is></c></row><row r='5'><c r='A5' t='inlineStr'><is><t>Vmp,hot61 (V)</t></is></c><c r='B5'><f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B8-25))</f></c><c r='C5' t='inlineStr'><is><t>per module</t></is></c></row><row r='6'><c r='A6' t='inlineStr'><is><t>Vmp,hot70 (V)</t></is></c><c r='B6'><f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B9-25))</f></c><c r='C6' t='inlineStr'><is><t>per module</t></is></c></row><row r='7'><c r='A7' t='inlineStr'><is><t>Vmp,cold (V)</t></is></c><c r='B7'><f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B7-25))</f></c><c r='C7' t='inlineStr'><is><t>per module</t></is></c></row><row r='8'><c r='A8' t='inlineStr'><is><t>Ns_min</t></is></c><c r='B8'><f>=CEILING('Parameters'!B18/B6,1)</f></c><c r='C8' t='inlineStr'><is><t>ceil(Vmppt_min/Vmp,hot70)</t></is></c></row><row r='9'><c r='A9' t='inlineStr'><is><t>Ns_max</t></is></c><c r='B9'><f>=FLOOR('Parameters'!B20/B4,1)</f></c><c r='C9' t='inlineStr'><is><t>floor(Vctrl_max/Voc,cold)</t></is></c></row><row r='10'><c r='A10' t='inlineStr'><is><t>Ns_choice</t></is></c><c r='B10'><f>='Parameters'!B27</f></c><c r='C10' t='inlineStr'><is><t>chosen series count</t></is></c></row><row r='11'><c r='A11' t='inlineStr'><is><t>Np_choice</t></is></c><c r='B11'><f>='Parameters'!B28</f></c><c r='C11' t='inlineStr'><is><t>chosen parallel count</t></is></c></row><row r='12'><c r='A12' t='inlineStr'><is><t>P_inst (kWp)</t></is></c><c r='B12'><f>=B10*B11*'Parameters'!B10/1000</f></c><c r='C12' t='inlineStr'><is><t>installed capacity</t></is></c></row><row r='13'><c r='A13' t='inlineStr'><is><t>Voc,cold涓?(V)</t></is></c><c r='B13'><f>=B4*B10</f></c><c r='C13' t='inlineStr'><is><t>string low-temp Voc</t></is></c></row><row r='14'><c r='A14' t='inlineStr'><is><t>Vmp,hot涓?1 (V)</t></is></c><c r='B14'><f>=B5*B10</f></c><c r='C14' t='inlineStr'><is><t>string MPPT V 61C</t></is></c></row><row r='15'><c r='A15' t='inlineStr'><is><t>Vmp,hot涓?0 (V)</t></is></c><c r='B15'><f>=B6*B10</f></c><c r='C15' t='inlineStr'><is><t>string MPPT V 70C</t></is></c></row><row r='16'><c r='A16' t='inlineStr'><is><t>Vmp,cold涓?(V)</t></is></c><c r='B16'><f>=B7*B10</f></c><c r='C16' t='inlineStr'><is><t>string MPPT V low temp</t></is></c></row><row r='17'><c r='A17' t='inlineStr'><is><t>I_mpp,array (A)</t></is></c><c r='B17'><f>='Parameters'!B14*B11</f></c><c r='C17' t='inlineStr'><is><t>array operating current</t></is></c></row><row r='18'><c r='A18' t='inlineStr'><is><t>I_sc,array (A)</t></is></c><c r='B18'><f>='Parameters'!B13*B11</f></c><c r='C18' t='inlineStr'><is><t>array short circuit current</t></is></c></row><row r='19'><c r='A19' t='inlineStr'><is><t>I_chg (A)</t></is></c><c r='B19'><f>=MIN(B12*1000*'Parameters'!B23/'Parameters'!B24,'Parameters'!B25)</f></c><c r='C19' t='inlineStr'><is><t>backfill W4 charge current</t></is></c></row><row r='20'><c r='A20' t='inlineStr'><is><t>Check1 Voc,cold涓?=Vctrl_max</t></is></c><c r='B20'><f>=IF(B13<='Parameters'!B20,'OK','FAIL')</f></c><c r='C20' t='inlineStr'><is><t></t></is></c></row><row r='21'><c r='A21' t='inlineStr'><is><t>Check2 Voc,cold涓?=Vmppt_max</t></is></c><c r='B21'><f>=IF(B13<='Parameters'!B19,'OK','FAIL')</f></c><c r='C21' t='inlineStr'><is><t></t></is></c></row><row r='22'><c r='A22' t='inlineStr'><is><t>Check3 Vmp,hot涓?0>=Vmppt_min</t></is></c><c r='B22'><f>=IF(B15>='Parameters'!B18,'OK','FAIL')</f></c><c r='C22' t='inlineStr'><is><t></t></is></c></row><row r='23'><c r='A23' t='inlineStr'><is><t>Check4 Vmp,cold涓?=Vmppt_max</t></is></c><c r='B23'><f>=IF(B16<='Parameters'!B19,'OK','FAIL')</f></c><c r='C23' t='inlineStr'><is><t></t></is></c></row><row r='24'><c r='A24' t='inlineStr'><is><t>Check5 I_sc,array<=limit</t></is></c><c r='B24'><f>=IF(B18<='Parameters'!B22,'OK','FAIL')</f></c><c r='C24' t='inlineStr'><is><t></t></is></c></row><row r='25'><c r='A25' t='inlineStr'><is><t>Check6 Pin<=P_ctrl_max</t></is></c><c r='B25'><f>=IF(B12*1000<='Parameters'!B21,'OK','FAIL')</f></c><c r='C25' t='inlineStr'><is><t></t></is></c></row><row r='26'><c r='A26' t='inlineStr'><is><t>Check7 I_chg<=I_bat_limit</t></is></c><c r='B26'><f>=IF(B19<='Parameters'!B26,'OK','FAIL')</f></c><c r='C26' t='inlineStr'><is><t></t></is></c></row><row r='28'><c r='A28' t='inlineStr'><is><t>Monthly energy check (P_PV=B11 kWp, eta_path=Parameters!B6)</t></is></c></row><row r='29'><c r='A29' t='inlineStr'><is><t>Month</t></is></c><c r='B29' t='inlineStr'><is><t>H_tilt(m)</t></is></c><c r='C29' t='inlineStr'><is><t>EPV(kWh/d)</t></is></c><c r='D29' t='inlineStr'><is><t>E_AC(kWh/d)</t></is></c><c r='E29' t='inlineStr'><is><t>Ratio</t></is></c><c r='F29' t='inlineStr'><is><t>Result</t></is></c></row><row r='30'><c r='A30'><v>1</v></c><c r='B30'><v>3.44</v></c><c r='C30'><f>=$B$12*B30*'Parameters'!$B$6</f></c><c r='D30'><v>3.61</v></c><c r='E30'><f>=IF(D30=0,0,C30/D30)</f></c><c r='F30'><f>=IF(C30>=D30,'OK','FAIL')</f></c></row><row r='31'><c r='A31'><v>2</v></c><c r='B31'><v>3.74</v></c><c r='C31'><f>=$B$12*B31*'Parameters'!$B$6</f></c><c r='D31'><v>3.61</v></c><c r='E31'><f>=IF(D31=0,0,C31/D31)</f></c><c r='F31'><f>=IF(C31>=D31,'OK','FAIL')</f></c></row><row r='32'><c r='A32'><v>3</v></c><c r='B32'><v>3.96</v></c><c r='C32'><f>=$B$12*B32*'Parameters'!$B$6</f></c><c r='D32'><v>3.61</v></c><c r='E32'><f>=IF(D32=0,0,C32/D32)</f></c><c r='F32'><f>=IF(C32>=D32,'OK','FAIL')</f></c></row><row r='33'><c r='A33'><v>4</v></c><c r='B33'><v>4.55</v></c><c r='C33'><f>=$B$12*B33*'Parameters'!$B$6</f></c><c r='D33'><v>3.61</v></c><c r='E33'><f>=IF(D33=0,0,C33/D33)</f></c><c r='F33'><f>=IF(C33>=D33,'OK','FAIL')</f></c></row><row r='34'><c r='A34'><v>5</v></c><c r='B34'><v>4.78</v></c><c r='C34'><f>=$B$12*B34*'Parameters'!$B$6</f></c><c r='D34'><v>6.99</v></c><c r='E34'><f>=IF(D34=0,0,C34/D34)</f></c><c r='F34'><f>=IF(C34>=D34,'OK','FAIL')</f></c></row><row r='35'><c r='A35'><v>6</v></c><c r='B35'><v>5.15</v></c><c r='C35'><f>=$B$12*B35*'Parameters'!$B$6</f></c><c r='D35'><v>6.99</v></c><c r='E35'><f>=IF(D35=0,0,C35/D35)</f></c><c r='F35'><f>=IF(C35>=D35,'OK','FAIL')</f></c></row><row r='36'><c r='A36'><v>7</v></c><c r='B36'><v>5.88</v></c><c r='C36'><f>=$B$12*B36*'Parameters'!$B$6</f></c><c r='D36'><v>6.99</v></c><c r='E36'><f>=IF(D36=0,0,C36/D36)</f></c><c r='F36'><f>=IF(C36>=D36,'OK','FAIL')</f></c></row><row r='37'><c r='A37'><v>8</v></c><c r='B37'><v>5.19</v></c><c r='C37'><f>=$B$12*B37*'Parameters'!$B$6</f></c><c r='D37'><v>6.99</v></c><c r='E37'><f>=IF(D37=0,0,C37/D37)</f></c><c r='F37'><f>=IF(C37>=D37,'OK','FAIL')</f></c></row><row r='38'><c r='A38'><v>9</v></c><c r='B38'><v>5.29</v></c><c r='C38'><f>=$B$12*B38*'Parameters'!$B$6</f></c><c r='D38'><v>6.99</v></c><c r='E38'><f>=IF(D38=0,0,C38/D38)</f></c><c r='F38'><f>=IF(C38>=D38,'OK','FAIL')</f></c></row><row r='39'><c r='A39'><v>10</v></c><c r='B39'><v>4.46</v></c><c r='C39'><f>=$B$12*B39*'Parameters'!$B$6</f></c><c r='D39'><v>6.99</v></c><c r='E39'><f>=IF(D39=0,0,C39/D39)</f></c><c r='F39'><f>=IF(C39>=D39,'OK','FAIL')</f></c></row><row r='40'><c r='A40'><v>11</v></c><c r='B40'><v>4.12</v></c><c r='C40'><f>=$B$12*B40*'Parameters'!$B$6</f></c><c r='D40'><v>3.61</v></c><c r='E40'><f>=IF(D40=0,0,C40/D40)</f></c><c r='F40'><f>=IF(C40>=D40,'OK','FAIL')</f></c></row><row r='41'><c r='A41'><v>12</v></c><c r='B41'><v>3.44</v></c><c r='C41'><f>=$B$12*B41*'Parameters'!$B$6</f></c><c r='D41'><v>3.61</v></c><c r='E41'><f>=IF(D41=0,0,C41/D41)</f></c><c r='F41'><f>=IF(C41>=D41,'OK','FAIL')</f></c></row></sheetData></worksheet>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PV array capacity calc and checks (Shenzhen W5, auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Formula/Value</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P_PV,min (kWp)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>='Parameters'!B3*'Parameters'!B4/('Parameters'!B5*'Parameters'!B6)</f>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>E_AC*K_PV/(H_tilt*eta_path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Voc,cold (V)</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>='Parameters'!B11*(1+'Parameters'!B15*('Parameters'!B7-25))</f>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>per module</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vmp,hot61 (V)</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B8-25))</f>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>per module</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vmp,hot70 (V)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B9-25))</f>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>per module</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vmp,cold (V)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B7-25))</f>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>per module</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ns_min</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>=CEILING('Parameters'!B18/B6,1)</f>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ceil(Vmppt_min/Vmp,hot70)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ns_max</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>=FLOOR('Parameters'!B20/B4,1)</f>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>floor(Vctrl_max/Voc,cold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ns_choice</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>='Parameters'!B27</f>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>chosen series count</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Np_choice</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>='Parameters'!B28</f>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chosen parallel count</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P_inst (kWp)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>=B10*B11*'Parameters'!B10/1000</f>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>installed capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Voc,cold string (V)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>=B4*B10</f>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>string low-temp Voc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vmp,hot string 61C (V)</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>=B5*B10</f>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>string MPPT V 61C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vmp,hot string 70C (V)</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>=B6*B10</f>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>string MPPT V 70C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vmp,cold string (V)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>=B7*B10</f>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>string MPPT V low temp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I_mpp,array (A)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>='Parameters'!B14*B11</f>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>array operating current</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I_sc,array (A)</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>='Parameters'!B13*B11</f>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>array short circuit current</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I_chg (A)</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>=MIN(B12*1000*'Parameters'!B23/'Parameters'!B24,'Parameters'!B25)</f>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>backfill W4 charge current</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Check1: Voc,cold string &lt;= Vctrl_max</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>=IF(B13&lt;='Parameters'!B20,'OK','FAIL')</f>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Check2: Voc,cold string &lt;= Vmppt_max</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>=IF(B13&lt;='Parameters'!B19,'OK','FAIL')</f>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Check3: Vmp,hot string 70C &gt;= Vmppt_min</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>=IF(B15&gt;='Parameters'!B18,'OK','FAIL')</f>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Check4: Vmp,cold string &lt;= Vmppt_max</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>=IF(B16&lt;='Parameters'!B19,'OK','FAIL')</f>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Check5 I_sc,array&lt;=limit</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>=IF(B18&lt;='Parameters'!B22,'OK','FAIL')</f>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Check6 Pin&lt;=P_ctrl_max</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>=IF(B12*1000&lt;='Parameters'!B21,'OK','FAIL')</f>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Check7 I_chg&lt;=I_bat_limit</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>=IF(B19&lt;='Parameters'!B26,'OK','FAIL')</f>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Monthly energy check (P_PV=B11 kWp, eta_path=Parameters!B6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H_tilt(m)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EPV(kWh/d)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>E_AC(kWh/d)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30">
+        <v>3.44</v>
+      </c>
+      <c r="C30">
+        <f>=$B$12*B30*'Parameters'!$B$6</f>
+      </c>
+      <c r="D30">
+        <v>3.61</v>
+      </c>
+      <c r="E30">
+        <f>=IF(D30=0,0,C30/D30)</f>
+      </c>
+      <c r="F30">
+        <f>=IF(C30&gt;=D30,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>3.74</v>
+      </c>
+      <c r="C31">
+        <f>=$B$12*B31*'Parameters'!$B$6</f>
+      </c>
+      <c r="D31">
+        <v>3.61</v>
+      </c>
+      <c r="E31">
+        <f>=IF(D31=0,0,C31/D31)</f>
+      </c>
+      <c r="F31">
+        <f>=IF(C31&gt;=D31,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>3.96</v>
+      </c>
+      <c r="C32">
+        <f>=$B$12*B32*'Parameters'!$B$6</f>
+      </c>
+      <c r="D32">
+        <v>3.61</v>
+      </c>
+      <c r="E32">
+        <f>=IF(D32=0,0,C32/D32)</f>
+      </c>
+      <c r="F32">
+        <f>=IF(C32&gt;=D32,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>4.55</v>
+      </c>
+      <c r="C33">
+        <f>=$B$12*B33*'Parameters'!$B$6</f>
+      </c>
+      <c r="D33">
+        <v>3.61</v>
+      </c>
+      <c r="E33">
+        <f>=IF(D33=0,0,C33/D33)</f>
+      </c>
+      <c r="F33">
+        <f>=IF(C33&gt;=D33,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34">
+        <v>4.78</v>
+      </c>
+      <c r="C34">
+        <f>=$B$12*B34*'Parameters'!$B$6</f>
+      </c>
+      <c r="D34">
+        <v>6.99</v>
+      </c>
+      <c r="E34">
+        <f>=IF(D34=0,0,C34/D34)</f>
+      </c>
+      <c r="F34">
+        <f>=IF(C34&gt;=D34,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35">
+        <v>5.15</v>
+      </c>
+      <c r="C35">
+        <f>=$B$12*B35*'Parameters'!$B$6</f>
+      </c>
+      <c r="D35">
+        <v>6.99</v>
+      </c>
+      <c r="E35">
+        <f>=IF(D35=0,0,C35/D35)</f>
+      </c>
+      <c r="F35">
+        <f>=IF(C35&gt;=D35,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>5.88</v>
+      </c>
+      <c r="C36">
+        <f>=$B$12*B36*'Parameters'!$B$6</f>
+      </c>
+      <c r="D36">
+        <v>6.99</v>
+      </c>
+      <c r="E36">
+        <f>=IF(D36=0,0,C36/D36)</f>
+      </c>
+      <c r="F36">
+        <f>=IF(C36&gt;=D36,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37">
+        <v>5.19</v>
+      </c>
+      <c r="C37">
+        <f>=$B$12*B37*'Parameters'!$B$6</f>
+      </c>
+      <c r="D37">
+        <v>6.99</v>
+      </c>
+      <c r="E37">
+        <f>=IF(D37=0,0,C37/D37)</f>
+      </c>
+      <c r="F37">
+        <f>=IF(C37&gt;=D37,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38">
+        <v>5.29</v>
+      </c>
+      <c r="C38">
+        <f>=$B$12*B38*'Parameters'!$B$6</f>
+      </c>
+      <c r="D38">
+        <v>6.99</v>
+      </c>
+      <c r="E38">
+        <f>=IF(D38=0,0,C38/D38)</f>
+      </c>
+      <c r="F38">
+        <f>=IF(C38&gt;=D38,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>4.46</v>
+      </c>
+      <c r="C39">
+        <f>=$B$12*B39*'Parameters'!$B$6</f>
+      </c>
+      <c r="D39">
+        <v>6.99</v>
+      </c>
+      <c r="E39">
+        <f>=IF(D39=0,0,C39/D39)</f>
+      </c>
+      <c r="F39">
+        <f>=IF(C39&gt;=D39,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>4.12</v>
+      </c>
+      <c r="C40">
+        <f>=$B$12*B40*'Parameters'!$B$6</f>
+      </c>
+      <c r="D40">
+        <v>3.61</v>
+      </c>
+      <c r="E40">
+        <f>=IF(D40=0,0,C40/D40)</f>
+      </c>
+      <c r="F40">
+        <f>=IF(C40&gt;=D40,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>12</v>
+      </c>
+      <c r="B41">
+        <v>3.44</v>
+      </c>
+      <c r="C41">
+        <f>=$B$12*B41*'Parameters'!$B$6</f>
+      </c>
+      <c r="D41">
+        <v>3.61</v>
+      </c>
+      <c r="E41">
+        <f>=IF(D41=0,0,C41/D41)</f>
+      </c>
+      <c r="F41">
+        <f>=IF(C41&gt;=D41,'OK','FAIL')</f>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r='1'><c r='A1' t='inlineStr'><is><t>PV array design check summary (Shenzhen W5)</t></is></c></row><row r='2'><c r='A2' t='inlineStr'><is><t>Item</t></is></c><c r='B2' t='inlineStr'><is><t>Calc</t></is></c><c r='C2' t='inlineStr'><is><t>Allowed</t></is></c><c r='D2' t='inlineStr'><is><t>Result</t></is></c></row><row r='3'><c r='A3' t='inlineStr'><is><t>Required capacity (kWp)</t></is></c><c r='B3'><f>='Calc'!B3</f></c><c r='C3' t='inlineStr'><is><t>-</t></is></c><c r='D3' t='inlineStr'><is><t>-</t></is></c></row><row r='4'><c r='A4' t='inlineStr'><is><t>Module model / power</t></is></c><c r='B4' t='inlineStr'><is><t>LONGi LR7-72HGD-600M x4</t></is></c><c r='C4' t='inlineStr'><is><t>-</t></is></c><c r='D4' t='inlineStr'><is><t>-</t></is></c></row><row r='5'><c r='A5' t='inlineStr'><is><t>Low-temp Voc string (V)</t></is></c><c r='B5'><f>='Calc'!B13</f></c><c r='C5' t='inlineStr'><is><t><=450</t></is></c><c r='D5'><f>=IF(B5<='Parameters'!B20,'OK','FAIL')</f></c></row><row r='6'><c r='A6' t='inlineStr'><is><t>Low-temp Voc string (V)</t></is></c><c r='B6'><f>='Calc'!B13</f></c><c r='C6' t='inlineStr'><is><t><=430 MPPT max</t></is></c><c r='D6'><f>=IF(B6<='Parameters'!B19,'OK','FAIL')</f></c></row><row r='7'><c r='A7' t='inlineStr'><is><t>Hot MPPT V string 70C (V)</t></is></c><c r='B7'><f>='Calc'!B15</f></c><c r='C7' t='inlineStr'><is><t>>=120</t></is></c><c r='D7'><f>=IF(B7>='Parameters'!B18,'OK','FAIL')</f></c></row><row r='8'><c r='A8' t='inlineStr'><is><t>Cold MPPT V string (V)</t></is></c><c r='B8'><f>='Calc'!B16</f></c><c r='C8' t='inlineStr'><is><t><=430</t></is></c><c r='D8'><f>=IF(B8<='Parameters'!B19,'OK','FAIL')</f></c></row><row r='9'><c r='A9' t='inlineStr'><is><t>Modules per string</t></is></c><c r='B9'><f>='Calc'!B10</f></c><c r='C9' t='inlineStr'><is><t>[4,8]</t></is></c><c r='D9'><f>=IF(AND(B9>='Calc'!B8,B9<='Calc'!B9),'OK','FAIL')</f></c></row><row r='10'><c r='A10' t='inlineStr'><is><t>Parallel strings</t></is></c><c r='B10'><f>='Calc'!B11</f></c><c r='C10' t='inlineStr'><is><t>-</t></is></c><c r='D10' t='inlineStr'><is><t>-</t></is></c></row><row r='11'><c r='A11' t='inlineStr'><is><t>Installed capacity (kWp)</t></is></c><c r='B11'><f>='Calc'!B12</f></c><c r='C11' t='inlineStr'><is><t><=6.0kW</t></is></c><c r='D11'><f>=IF(B11*1000<='Parameters'!B21,'OK','FAIL')</f></c></row><row r='12'><c r='A12' t='inlineStr'><is><t>Array Imp (A)</t></is></c><c r='B12'><f>='Calc'!B17</f></c><c r='C12' t='inlineStr'><is><t><=per-MPPT</t></is></c><c r='D12'><f>=IF(B12<='Parameters'!B22,'OK','FAIL')</f></c></row><row r='13'><c r='A13' t='inlineStr'><is><t>Array Isc (A)</t></is></c><c r='B13'><f>='Calc'!B18</f></c><c r='C13' t='inlineStr'><is><t><=per-MPPT</t></is></c><c r='D13'><f>=IF(B13<='Parameters'!B22,'OK','FAIL')</f></c></row><row r='14'><c r='A14' t='inlineStr'><is><t>I_chg backfill W4 (A)</t></is></c><c r='B14'><f>='Calc'!B19</f></c><c r='C14' t='inlineStr'><is><t><=200 (4x50A)</t></is></c><c r='D14'><f>=IF(B14<='Parameters'!B26,'OK','FAIL')</f></c></row></sheetData></worksheet>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PV array design check summary (Shenzhen W5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Calc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Required capacity (kWp)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>='Calc'!B3</f>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Module model / power</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LONGi LR7-72HGD-600M x4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low-temp Voc string (V)</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>='Calc'!B13</f>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;=450</t>
+        </is>
+      </c>
+      <c r="D5">
+        <f>=IF(B5&lt;='Parameters'!B20,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Low-temp Voc string (V)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>='Calc'!B13</f>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;=430 MPPT max</t>
+        </is>
+      </c>
+      <c r="D6">
+        <f>=IF(B6&lt;='Parameters'!B19,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hot MPPT V string 70C (V)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>='Calc'!B15</f>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>&gt;=120</t>
+        </is>
+      </c>
+      <c r="D7">
+        <f>=IF(B7&gt;='Parameters'!B18,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cold MPPT V string (V)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>='Calc'!B16</f>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>&lt;=430</t>
+        </is>
+      </c>
+      <c r="D8">
+        <f>=IF(B8&lt;='Parameters'!B19,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Modules per string</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>='Calc'!B10</f>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[4,8]</t>
+        </is>
+      </c>
+      <c r="D9">
+        <f>=IF(AND(B9&gt;='Calc'!B8,B9&lt;='Calc'!B9),'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Parallel strings</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>='Calc'!B11</f>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Installed capacity (kWp)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>='Calc'!B12</f>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;=6.0kW</t>
+        </is>
+      </c>
+      <c r="D11">
+        <f>=IF(B11*1000&lt;='Parameters'!B21,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Array Imp (A)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>='Calc'!B17</f>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>&lt;=per-MPPT</t>
+        </is>
+      </c>
+      <c r="D12">
+        <f>=IF(B12&lt;='Parameters'!B22,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Array Isc (A)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>='Calc'!B18</f>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>&lt;=per-MPPT</t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>=IF(B13&lt;='Parameters'!B22,'OK','FAIL')</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I_chg backfill W4 (A)</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>='Calc'!B19</f>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&lt;=200 (4x50A)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <f>=IF(B14&lt;='Parameters'!B26,'OK','FAIL')</f>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/计算-光伏阵列-深圳.xlsx
+++ b/docs/计算-光伏阵列-深圳.xlsx
@@ -1,16 +1,417 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Parameters" sheetId="1" r:id="rId1"/>
-    <sheet name="Calc" sheetId="2" r:id="rId2"/>
-    <sheet name="Check" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -42,7 +443,7 @@
           <t>E_AC (kWh/d)</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>6.99</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -57,7 +458,7 @@
           <t>K_PV</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>1.1</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -72,7 +473,7 @@
           <t>H_tilt (h/d)</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>4.46</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -87,12 +488,12 @@
           <t>eta_path</t>
         </is>
       </c>
-      <c r="B6">
-        <v>0.77</v>
+      <c r="B6" t="n">
+        <v>0.782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>W3 combined efficiency</t>
+          <t>W3 combined efficiency (W6 backfill eta_inv=0.93)</t>
         </is>
       </c>
     </row>
@@ -102,7 +503,7 @@
           <t>T_min (C)</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>0.2</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -117,7 +518,7 @@
           <t>T_cell_hot (C)</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>61</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -132,7 +533,7 @@
           <t>T_cell_extreme (C)</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>70</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -147,7 +548,7 @@
           <t>P_mpp (W)</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>600</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -162,7 +563,7 @@
           <t>Voc_STC (V)</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>52.22</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -177,7 +578,7 @@
           <t>Vmp_STC (V)</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>44.12</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -192,7 +593,7 @@
           <t>Isc_STC (A)</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>14.49</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -207,7 +608,7 @@
           <t>Imp_STC (A)</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>13.6</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -222,7 +623,7 @@
           <t>bVoc (1/C)</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>-0.0023</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -237,7 +638,7 @@
           <t>bVmp (1/C)</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>-0.0028</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -252,7 +653,7 @@
           <t>NOCT (C)</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>45</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -267,7 +668,7 @@
           <t>V_mppt_min (V)</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>120</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -282,7 +683,7 @@
           <t>V_mppt_max (V)</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>430</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -297,12 +698,12 @@
           <t>V_ctrl_max (V)</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>450</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>max PV input (W6)</t>
+          <t>max PV input (W6 confirmed, official datasheet)</t>
         </is>
       </c>
     </row>
@@ -312,12 +713,12 @@
           <t>P_ctrl_max (W)</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>6000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>max PV input power</t>
+          <t>max PV input power (W6 confirmed)</t>
         </is>
       </c>
     </row>
@@ -327,12 +728,12 @@
           <t>I_sc_limit (A)</t>
         </is>
       </c>
-      <c r="B22">
-        <v>15</v>
+      <c r="B22" t="n">
+        <v>22</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>per MPPT Isc limit (W6)</t>
+          <t>per MPPT input current limit (W6 confirmed, official 22A)</t>
         </is>
       </c>
     </row>
@@ -342,7 +743,7 @@
           <t>eta_MPPT</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>0.96</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -357,7 +758,7 @@
           <t>V_bat_chg (V)</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>54.4</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -372,12 +773,12 @@
           <t>I_ctrl_out_max (A)</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MPPT output limit (W6)</t>
+          <t>max solar charge current 100A (W6 confirmed)</t>
         </is>
       </c>
     </row>
@@ -387,7 +788,7 @@
           <t>I_bat_chg_limit (A)</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>200</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -402,7 +803,7 @@
           <t>Ns_choice</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -417,7 +818,7 @@
           <t>Np_choice</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -427,11 +828,18 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -465,6 +873,7 @@
       </c>
       <c r="B3">
         <f>='Parameters'!B3*'Parameters'!B4/('Parameters'!B5*'Parameters'!B6)</f>
+        <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -480,6 +889,7 @@
       </c>
       <c r="B4">
         <f>='Parameters'!B11*(1+'Parameters'!B15*('Parameters'!B7-25))</f>
+        <v/>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -495,6 +905,7 @@
       </c>
       <c r="B5">
         <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B8-25))</f>
+        <v/>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -510,6 +921,7 @@
       </c>
       <c r="B6">
         <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B9-25))</f>
+        <v/>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -525,6 +937,7 @@
       </c>
       <c r="B7">
         <f>='Parameters'!B12*(1+'Parameters'!B16*('Parameters'!B7-25))</f>
+        <v/>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -540,6 +953,7 @@
       </c>
       <c r="B8">
         <f>=CEILING('Parameters'!B18/B6,1)</f>
+        <v/>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -555,6 +969,7 @@
       </c>
       <c r="B9">
         <f>=FLOOR('Parameters'!B20/B4,1)</f>
+        <v/>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -570,6 +985,7 @@
       </c>
       <c r="B10">
         <f>='Parameters'!B27</f>
+        <v/>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -585,6 +1001,7 @@
       </c>
       <c r="B11">
         <f>='Parameters'!B28</f>
+        <v/>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -600,6 +1017,7 @@
       </c>
       <c r="B12">
         <f>=B10*B11*'Parameters'!B10/1000</f>
+        <v/>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -615,6 +1033,7 @@
       </c>
       <c r="B13">
         <f>=B4*B10</f>
+        <v/>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -630,6 +1049,7 @@
       </c>
       <c r="B14">
         <f>=B5*B10</f>
+        <v/>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -645,6 +1065,7 @@
       </c>
       <c r="B15">
         <f>=B6*B10</f>
+        <v/>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -660,6 +1081,7 @@
       </c>
       <c r="B16">
         <f>=B7*B10</f>
+        <v/>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -675,6 +1097,7 @@
       </c>
       <c r="B17">
         <f>='Parameters'!B14*B11</f>
+        <v/>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -690,6 +1113,7 @@
       </c>
       <c r="B18">
         <f>='Parameters'!B13*B11</f>
+        <v/>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -705,6 +1129,7 @@
       </c>
       <c r="B19">
         <f>=MIN(B12*1000*'Parameters'!B23/'Parameters'!B24,'Parameters'!B25)</f>
+        <v/>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -720,12 +1145,9 @@
       </c>
       <c r="B20">
         <f>=IF(B13&lt;='Parameters'!B20,'OK','FAIL')</f>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -735,12 +1157,9 @@
       </c>
       <c r="B21">
         <f>=IF(B13&lt;='Parameters'!B19,'OK','FAIL')</f>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -750,12 +1169,9 @@
       </c>
       <c r="B22">
         <f>=IF(B15&gt;='Parameters'!B18,'OK','FAIL')</f>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -765,12 +1181,9 @@
       </c>
       <c r="B23">
         <f>=IF(B16&lt;='Parameters'!B19,'OK','FAIL')</f>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -780,12 +1193,9 @@
       </c>
       <c r="B24">
         <f>=IF(B18&lt;='Parameters'!B22,'OK','FAIL')</f>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -795,12 +1205,9 @@
       </c>
       <c r="B25">
         <f>=IF(B12*1000&lt;='Parameters'!B21,'OK','FAIL')</f>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -810,12 +1217,9 @@
       </c>
       <c r="B26">
         <f>=IF(B19&lt;='Parameters'!B26,'OK','FAIL')</f>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -857,251 +1261,294 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="n">
         <v>1</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>3.44</v>
       </c>
       <c r="C30">
         <f>=$B$12*B30*'Parameters'!$B$6</f>
-      </c>
-      <c r="D30">
+        <v/>
+      </c>
+      <c r="D30" t="n">
         <v>3.61</v>
       </c>
       <c r="E30">
         <f>=IF(D30=0,0,C30/D30)</f>
+        <v/>
       </c>
       <c r="F30">
         <f>=IF(C30&gt;=D30,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="n">
         <v>2</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>3.74</v>
       </c>
       <c r="C31">
         <f>=$B$12*B31*'Parameters'!$B$6</f>
-      </c>
-      <c r="D31">
+        <v/>
+      </c>
+      <c r="D31" t="n">
         <v>3.61</v>
       </c>
       <c r="E31">
         <f>=IF(D31=0,0,C31/D31)</f>
+        <v/>
       </c>
       <c r="F31">
         <f>=IF(C31&gt;=D31,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="n">
         <v>3</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>3.96</v>
       </c>
       <c r="C32">
         <f>=$B$12*B32*'Parameters'!$B$6</f>
-      </c>
-      <c r="D32">
+        <v/>
+      </c>
+      <c r="D32" t="n">
         <v>3.61</v>
       </c>
       <c r="E32">
         <f>=IF(D32=0,0,C32/D32)</f>
+        <v/>
       </c>
       <c r="F32">
         <f>=IF(C32&gt;=D32,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="n">
         <v>4</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="n">
         <v>4.55</v>
       </c>
       <c r="C33">
         <f>=$B$12*B33*'Parameters'!$B$6</f>
-      </c>
-      <c r="D33">
+        <v/>
+      </c>
+      <c r="D33" t="n">
         <v>3.61</v>
       </c>
       <c r="E33">
         <f>=IF(D33=0,0,C33/D33)</f>
+        <v/>
       </c>
       <c r="F33">
         <f>=IF(C33&gt;=D33,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="n">
         <v>5</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="n">
         <v>4.78</v>
       </c>
       <c r="C34">
         <f>=$B$12*B34*'Parameters'!$B$6</f>
-      </c>
-      <c r="D34">
+        <v/>
+      </c>
+      <c r="D34" t="n">
         <v>6.99</v>
       </c>
       <c r="E34">
         <f>=IF(D34=0,0,C34/D34)</f>
+        <v/>
       </c>
       <c r="F34">
         <f>=IF(C34&gt;=D34,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="n">
         <v>6</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="n">
         <v>5.15</v>
       </c>
       <c r="C35">
         <f>=$B$12*B35*'Parameters'!$B$6</f>
-      </c>
-      <c r="D35">
+        <v/>
+      </c>
+      <c r="D35" t="n">
         <v>6.99</v>
       </c>
       <c r="E35">
         <f>=IF(D35=0,0,C35/D35)</f>
+        <v/>
       </c>
       <c r="F35">
         <f>=IF(C35&gt;=D35,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="n">
         <v>7</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="n">
         <v>5.88</v>
       </c>
       <c r="C36">
         <f>=$B$12*B36*'Parameters'!$B$6</f>
-      </c>
-      <c r="D36">
+        <v/>
+      </c>
+      <c r="D36" t="n">
         <v>6.99</v>
       </c>
       <c r="E36">
         <f>=IF(D36=0,0,C36/D36)</f>
+        <v/>
       </c>
       <c r="F36">
         <f>=IF(C36&gt;=D36,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="n">
         <v>8</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="n">
         <v>5.19</v>
       </c>
       <c r="C37">
         <f>=$B$12*B37*'Parameters'!$B$6</f>
-      </c>
-      <c r="D37">
+        <v/>
+      </c>
+      <c r="D37" t="n">
         <v>6.99</v>
       </c>
       <c r="E37">
         <f>=IF(D37=0,0,C37/D37)</f>
+        <v/>
       </c>
       <c r="F37">
         <f>=IF(C37&gt;=D37,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="n">
         <v>9</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="n">
         <v>5.29</v>
       </c>
       <c r="C38">
         <f>=$B$12*B38*'Parameters'!$B$6</f>
-      </c>
-      <c r="D38">
+        <v/>
+      </c>
+      <c r="D38" t="n">
         <v>6.99</v>
       </c>
       <c r="E38">
         <f>=IF(D38=0,0,C38/D38)</f>
+        <v/>
       </c>
       <c r="F38">
         <f>=IF(C38&gt;=D38,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="n">
         <v>10</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="n">
         <v>4.46</v>
       </c>
       <c r="C39">
         <f>=$B$12*B39*'Parameters'!$B$6</f>
-      </c>
-      <c r="D39">
+        <v/>
+      </c>
+      <c r="D39" t="n">
         <v>6.99</v>
       </c>
       <c r="E39">
         <f>=IF(D39=0,0,C39/D39)</f>
+        <v/>
       </c>
       <c r="F39">
         <f>=IF(C39&gt;=D39,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="n">
         <v>11</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="n">
         <v>4.12</v>
       </c>
       <c r="C40">
         <f>=$B$12*B40*'Parameters'!$B$6</f>
-      </c>
-      <c r="D40">
+        <v/>
+      </c>
+      <c r="D40" t="n">
         <v>3.61</v>
       </c>
       <c r="E40">
         <f>=IF(D40=0,0,C40/D40)</f>
+        <v/>
       </c>
       <c r="F40">
         <f>=IF(C40&gt;=D40,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="n">
         <v>12</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="n">
         <v>3.44</v>
       </c>
       <c r="C41">
         <f>=$B$12*B41*'Parameters'!$B$6</f>
-      </c>
-      <c r="D41">
+        <v/>
+      </c>
+      <c r="D41" t="n">
         <v>3.61</v>
       </c>
       <c r="E41">
         <f>=IF(D41=0,0,C41/D41)</f>
+        <v/>
       </c>
       <c r="F41">
         <f>=IF(C41&gt;=D41,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1140,6 +1587,7 @@
       </c>
       <c r="B3">
         <f>='Calc'!B3</f>
+        <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1182,6 +1630,7 @@
       </c>
       <c r="B5">
         <f>='Calc'!B13</f>
+        <v/>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1190,6 +1639,7 @@
       </c>
       <c r="D5">
         <f>=IF(B5&lt;='Parameters'!B20,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1200,6 +1650,7 @@
       </c>
       <c r="B6">
         <f>='Calc'!B13</f>
+        <v/>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,6 +1659,7 @@
       </c>
       <c r="D6">
         <f>=IF(B6&lt;='Parameters'!B19,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1218,6 +1670,7 @@
       </c>
       <c r="B7">
         <f>='Calc'!B15</f>
+        <v/>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,6 +1679,7 @@
       </c>
       <c r="D7">
         <f>=IF(B7&gt;='Parameters'!B18,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1236,6 +1690,7 @@
       </c>
       <c r="B8">
         <f>='Calc'!B16</f>
+        <v/>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1244,6 +1699,7 @@
       </c>
       <c r="D8">
         <f>=IF(B8&lt;='Parameters'!B19,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1254,6 +1710,7 @@
       </c>
       <c r="B9">
         <f>='Calc'!B10</f>
+        <v/>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1262,6 +1719,7 @@
       </c>
       <c r="D9">
         <f>=IF(AND(B9&gt;='Calc'!B8,B9&lt;='Calc'!B9),'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1272,6 +1730,7 @@
       </c>
       <c r="B10">
         <f>='Calc'!B11</f>
+        <v/>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1292,6 +1751,7 @@
       </c>
       <c r="B11">
         <f>='Calc'!B12</f>
+        <v/>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1300,6 +1760,7 @@
       </c>
       <c r="D11">
         <f>=IF(B11*1000&lt;='Parameters'!B21,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1310,6 +1771,7 @@
       </c>
       <c r="B12">
         <f>='Calc'!B17</f>
+        <v/>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1318,6 +1780,7 @@
       </c>
       <c r="D12">
         <f>=IF(B12&lt;='Parameters'!B22,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1328,6 +1791,7 @@
       </c>
       <c r="B13">
         <f>='Calc'!B18</f>
+        <v/>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1336,6 +1800,7 @@
       </c>
       <c r="D13">
         <f>=IF(B13&lt;='Parameters'!B22,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1346,6 +1811,7 @@
       </c>
       <c r="B14">
         <f>='Calc'!B19</f>
+        <v/>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1354,8 +1820,10 @@
       </c>
       <c r="D14">
         <f>=IF(B14&lt;='Parameters'!B26,'OK','FAIL')</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>